--- a/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.90%637,000</t>
+          <t>14.78%637,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.90%</t>
+          <t>14.78%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.58%706,000</t>
+          <t>4.63%706,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.96%361.5</t>
+          <t>-0.69%144</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>361.5</v>
+        <v>144</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.17%1,222,000</t>
+          <t>4.05%2,980,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1222000</v>
+        <v>2980000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.34%145</t>
+          <t>-0.95%104.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>145</v>
+        <v>104.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.06%2,980,000</t>
+          <t>3.91%3,954,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2980000</v>
+        <v>3954000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,34 +748,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%105.5</t>
+          <t>+0.14%362</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>105.5</v>
+        <v>362</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.90%3,954,000</t>
+          <t>3.49%1,030,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3954000</v>
+        <v>1030000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.25%67,000</t>
+          <t>3.32%67,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3%722</t>
+          <t>+1.11%730</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.16%482,000</t>
+          <t>3.26%482,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.64%1555</t>
+          <t>-2.89%1510</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1555</v>
+        <v>1510</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.08%210,000</t>
+          <t>3.06%210,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.91%62,000</t>
+          <t>2.94%62,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>250.5</v>
+        <v>3400</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.45%1,021,000</t>
+          <t>2.37%71,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1021000</v>
+        <v>71000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3555</v>
+        <v>2100</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.31%71,000</t>
+          <t>2.26%114,036</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>71000</v>
+        <v>114036</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2115</v>
+        <v>1835</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.25%114,036</t>
+          <t>2.15%120,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>114036</v>
+        <v>120000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1240</v>
+        <v>250.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.17%192,000</t>
+          <t>2.00%853,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>192000</v>
+        <v>853000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1910</v>
+        <v>548</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.13%120,000</t>
+          <t>1.78%327,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>120000</v>
+        <v>327000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:08</t>
+          <t>2026-09-29 22:55:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.15%68.5</t>
+          <t>-0.33%151</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>68.5</v>
+        <v>151</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.86%2,904,000</t>
+          <t>1.72%1,213,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2904000</v>
+        <v>1213000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>580</v>
+        <v>1165</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.75%327,000</t>
+          <t>1.70%153,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>327000</v>
+        <v>153000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.33%151.5</t>
+          <t>-0.99%20.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>151.5</v>
+        <v>20.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%1,213,000</t>
+          <t>1.67%8,783,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1213000</v>
+        <v>8783000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.73%20.3</t>
+          <t>-2.06%238</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>20.3</v>
+        <v>238</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.68%8,783,000</t>
+          <t>1.65%726,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>8783000</v>
+        <v>726000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>962</v>
+        <v>2445</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.66%196,000</t>
+          <t>1.62%74,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>196000</v>
+        <v>74000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>+3.46%1195</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.66%153,000</t>
+          <t>1.49%138,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>153000</v>
+        <v>138000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%243</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>243</v>
+        <v>1270</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.65%726,000</t>
+          <t>1.49%128,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>726000</v>
+        <v>128000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-0.51%1960</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2340</v>
+        <v>1960</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.62%74,000</t>
+          <t>1.48%80,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>74000</v>
+        <v>80000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.7%1155</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1155</v>
+        <v>1810</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.52%138,000</t>
+          <t>1.42%80,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>138000</v>
+        <v>80000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.03%1970</t>
+          <t>0%68.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1970</v>
+        <v>68.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.46%80,000</t>
+          <t>1.40%2,177,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>80000</v>
+        <v>2177000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1895</v>
+        <v>945</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.42%80,000</t>
+          <t>1.27%143,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>80000</v>
+        <v>143000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>-0.81%73.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>948</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.27%143,000</t>
+          <t>1.16%1,657,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>143000</v>
+        <v>1657000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.19%74.5</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>74.5</v>
+        <v>153.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.17%1,657,000</t>
+          <t>1.11%766,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1657000</v>
+        <v>766000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>154</v>
+        <v>955</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.15%766,000</t>
+          <t>1.06%118,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>766000</v>
+        <v>118000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>-2.25%3685</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1530</v>
+        <v>3685</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.10%76,000</t>
+          <t>1.03%29,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>76000</v>
+        <v>29000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:09</t>
+          <t>2026-09-29 22:55:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.27%3770</t>
+          <t>-1.79%493</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3770</v>
+        <v>493</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.02%29,000</t>
+          <t>1.02%217,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>29000</v>
+        <v>217000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.01%502</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>502</v>
+        <v>6020</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.01%217,000</t>
+          <t>1.00%17,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>217000</v>
+        <v>17000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5670</v>
+        <v>2650</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.01%18,000</t>
+          <t>0.96%38,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>18000</v>
+        <v>38000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6245</v>
+        <v>5585</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.98%17,000</t>
+          <t>0.96%18,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.96%1500</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2700</v>
+        <v>1500</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.95%38,000</t>
+          <t>0.96%67,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>38000</v>
+        <v>67000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.99%1530</t>
+          <t>-0.95%47.15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1530</v>
+        <v>47.15</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.95%67,000</t>
+          <t>0.94%2,097,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>67000</v>
+        <v>2097000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.94%43,000</t>
+          <t>0.93%43,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.15%47.6</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47.6</v>
+        <v>6895</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.91%2,097,000</t>
+          <t>0.84%13,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2097000</v>
+        <v>13000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-3.1%814</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6920</v>
+        <v>814</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.78%13,000</t>
+          <t>0.80%102,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>13000</v>
+        <v>102000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1195</v>
+        <v>1585</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.68%60,000</t>
+          <t>0.79%55,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.58%64.1</t>
+          <t>-6.45%929</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>64.09999999999999</v>
+        <v>929</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.65%1,103,000</t>
+          <t>0.71%76,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1103000</v>
+        <v>76000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.58%171.5</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>171.5</v>
+        <v>1310</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.39%243,000</t>
+          <t>0.67%60,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>243000</v>
+        <v>60000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.78%64.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>503</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.38%79,000</t>
+          <t>0.66%1,103,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>79000</v>
+        <v>1103000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.47%213.5</t>
+          <t>+1.46%174</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>213.5</v>
+        <v>174</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.28%141,000</t>
+          <t>0.39%243,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>141000</v>
+        <v>243000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.9%2410</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2410</v>
+        <v>506</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.27%12,000</t>
+          <t>0.37%79,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>12000</v>
+        <v>79000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:10</t>
+          <t>2026-09-29 22:55:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>3324雙鴻</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.96%150</t>
+          <t>-4.68%1630</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>150</v>
+        <v>1630</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.20%139,000</t>
+          <t>0.29%18,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>139000</v>
+        <v>18000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:11</t>
+          <t>2026-09-29 22:55:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.58%68.5</t>
+          <t>-2.34%208.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>68.5</v>
+        <v>208.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.19%297,000</t>
+          <t>0.28%141,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>297000</v>
+        <v>141000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:11</t>
+          <t>2026-09-29 22:55:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>+2.7%2475</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12350</v>
+        <v>2475</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.12%1,000</t>
+          <t>0.27%12,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:11</t>
+          <t>2026-09-29 22:55:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>+1%151.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2125</v>
+        <v>151.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.20%139,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>139000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:11</t>
+          <t>2026-09-29 22:55:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,30 +3432,30 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1105</v>
+        <v>12115</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.12%1,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:11</t>
+          <t>2026-09-29 22:55:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,30 +3493,30 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.49%207</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>207</v>
+        <v>1120</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K51" t="n">

--- a/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:19</t>
+          <t>2026-09-29 23:06:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:20</t>
+          <t>2026-09-29 23:06:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:21</t>
+          <t>2026-09-29 23:06:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:22</t>
+          <t>2026-09-29 23:06:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:22</t>
+          <t>2026-09-29 23:06:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:22</t>
+          <t>2026-09-29 23:06:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:22</t>
+          <t>2026-09-29 23:06:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:22</t>
+          <t>2026-09-29 23:06:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
